--- a/stories/arbres/ATOM-EMO.LEX.005-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Garance construit une tour dans la chambre. Papa range des livres. Sami pose un cube trop vite. La tour tombe. Garance sent son visage chaud. Son ventre est dur. Garance dit : je suis en colère. Elle ouvre les doigts. Les mains restent loin. Garance peut s'éloigner. Elle s'éloigne vers le tapis. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte. Garance dit : papa, je suis en colère. La tour est tombée. Papa écoute. Plus tard, à la cuisine, Sami prend la cuillère de Garance. Garance sent encore la chaleur. Elle se souvient. Elle dit : je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Papa dit : tu as nommé. Tu as repris le geste. Même leçon, autre lieu. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+          <t>Garance construit une tour dans la chambre. Papa range des livres. Sami pose un cube trop vite. La tour tombe. Garance sent son visage chaud. Son ventre est dur. Je suis en colère. Elle ouvre les doigts. Les mains restent loin. Garance peut s'éloigner. Elle s'éloigne vers le tapis. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte. Papa, je suis en colère. La tour est tombée. Papa écoute. Plus tard, à la cuisine, Sami prend la cuillère de Garance. Garance sent encore la chaleur. Elle se souvient. Je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Tu as nommé. Tu as repris le geste. Même leçon, autre lieu. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Garance construit une tour dans la chambre. Papa range des livres. Sami pose un cube trop vite. La tour tombe. Garance sent son visage chaud. Son ventre est dur.
+enfant-f|Je suis en colère. Elle ouvre les doigts.
+narrateur|Les mains restent loin. Garance peut s'éloigner. Elle s'éloigne vers le tapis. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte.
+enfant-f|Papa, je suis en colère.
+narrateur|La tour est tombée. Papa écoute. Plus tard, à la cuisine, Sami prend la cuillère de Garance. Garance sent encore la chaleur. Elle se souvient.
+narrateur|Je suis en colère.
+narrateur|Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle.
+papa|Tu as nommé. Tu as repris le geste. Même leçon, autre lieu.
+narrateur|La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1498,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La tour de Garance tombe. Que fait-elle de sa colère ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Garance a nommé sa colère. Mains loin. Elle peut s'éloigner. Elle va vers papa, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1834,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Garance s'assoit près de papa. La tour reste au sol.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2001,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,7 @@
 narrateur|La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1505,6 +1511,7 @@
           <t>narrateur|La tour de Garance tombe. Que fait-elle de sa colère ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1683,7 @@
           <t>narrateur|Garance a nommé sa colère. Mains loin. Elle peut s'éloigner. Elle va vers papa, l'adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Garance s'assoit près de papa. La tour reste au sol.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.005-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Garance nomme sa colère deux fois</t>
+          <t>La tour de Nina</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,7 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +831,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina construit une tour. Un cube tombe. Elle nomme sa colère, s'éloigne, rejoint papa. À la cuisine, la cuillère part. Elle reprend le geste.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1185,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Garance construit une tour dans la chambre. Papa range des livres. Sami pose un cube trop vite. La tour tombe. Garance sent son visage chaud. Son ventre est dur. Je suis en colère. Elle ouvre les doigts. Les mains restent loin. Garance peut s'éloigner. Elle s'éloigne vers le tapis. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte. Papa, je suis en colère. La tour est tombée. Papa écoute. Plus tard, à la cuisine, Sami prend la cuillère de Garance. Garance sent encore la chaleur. Elle se souvient. Je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Tu as nommé. Tu as repris le geste. Même leçon, autre lieu. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+          <t>Un rayon jaune traverse la chambre. La poussière danse au-dessus du tapis. Une chaussette attend près du lit. Elle est un peu retournée. Une pile de livres penche contre le mur. Les livres sentent le papier chaud. Des cubes en bois sont au milieu. Le bois sent la forêt, tout doux. Nina, je range les livres. Moi, je fais une tour. Une tour bien droite ? Oui, papa. En ce moment, Nina pose un cube. Puis un autre. La tour monte. Victorino est là, près du tapis. Papa empile encore un livre. Le rouge tout en haut. Tu y es presque. Victorino pose un cube trop vite. La tour tombe. Les cubes roulent. Nina sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Elle ouvre les doigts. Les mains restent loin de Victorino. Nina peut s'éloigner. Elle s'éloigne vers le tapis du lit. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte près des livres. Papa, je suis en colère. La tour est tombée. Tu as dit le nom. Tu es en colère. Bravo, Nina. Tes mains sont restées loin. Tu t'es éloignée. Tu es venue vers moi. Tu as fait du bon travail. Tu veux souffler encore ? Oui, papa. Nina souffle. Le rayon tient encore la poussière. Plus tard, à la cuisine, la table est tiède. Ça sent le lait chaud. Nina a une petite cuillère. Victorino prend la cuillère de Nina. Nina sent encore la chaleur. Elle se souvient. Je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Papa, je suis en colère encore. Tu as nommé. Tu as repris le geste. Même leçon, autre lieu. Bravo. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1325,73 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Garance construit une tour dans la chambre. Papa range des livres. Sami pose un cube trop vite. La tour tombe. Garance sent son visage chaud. Son ventre est dur.
-enfant-f|Je suis en colère. Elle ouvre les doigts.
-narrateur|Les mains restent loin. Garance peut s'éloigner. Elle s'éloigne vers le tapis. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte.
+          <t>narrateur|Un rayon jaune traverse la chambre.
+narrateur|La poussière danse au-dessus du tapis.
+narrateur|Une chaussette attend près du lit.
+narrateur|Elle est un peu retournée.
+narrateur|Une pile de livres penche contre le mur.
+narrateur|Les livres sentent le papier chaud.
+narrateur|Des cubes en bois sont au milieu.
+narrateur|Le bois sent la forêt, tout doux.
+papa|Nina, je range les livres.
+enfant-f|Moi, je fais une tour.
+papa|Une tour bien droite ?
+enfant-f|Oui, papa.
+narrateur|En ce moment, Nina pose un cube.
+narrateur|Puis un autre.
+narrateur|La tour monte.
+narrateur|Victorino est là, près du tapis.
+narrateur|Papa empile encore un livre.
+enfant-f|Le rouge tout en haut.
+papa|Tu y es presque.
+narrateur|Victorino pose un cube trop vite.
+narrateur|La tour tombe.
+narrateur|Les cubes roulent.
+narrateur|Nina sent son visage chaud.
+narrateur|Son ventre est dur.
+narrateur|Être en colère, ce n'est pas honteux.
+enfant-f|Je suis en colère.
+narrateur|Elle ouvre les doigts.
+narrateur|Les mains restent loin de Victorino.
+narrateur|Nina peut s'éloigner.
+narrateur|Elle s'éloigne vers le tapis du lit.
+narrateur|Elle souffle trois fois.
+narrateur|Puis elle va vers papa.
+narrateur|Papa est l'adulte près des livres.
 enfant-f|Papa, je suis en colère.
-narrateur|La tour est tombée. Papa écoute. Plus tard, à la cuisine, Sami prend la cuillère de Garance. Garance sent encore la chaleur. Elle se souvient.
-narrateur|Je suis en colère.
-narrateur|Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle.
-papa|Tu as nommé. Tu as repris le geste. Même leçon, autre lieu.
-narrateur|La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+enfant-f|La tour est tombée.
+papa|Tu as dit le nom.
+papa|Tu es en colère.
+papa|Bravo, Nina.
+papa|Tes mains sont restées loin.
+papa|Tu t'es éloignée.
+papa|Tu es venue vers moi.
+papa|Tu as fait du bon travail.
+papa|Tu veux souffler encore ?
+enfant-f|Oui, papa.
+narrateur|Nina souffle.
+narrateur|Le rayon tient encore la poussière.
+narrateur|Plus tard, à la cuisine, la table est tiède.
+narrateur|Ça sent le lait chaud.
+narrateur|Nina a une petite cuillère.
+narrateur|Victorino prend la cuillère de Nina.
+narrateur|Nina sent encore la chaleur.
+narrateur|Elle se souvient.
+enfant-f|Je suis en colère.
+narrateur|Les mains restent loin.
+narrateur|Elle peut s'éloigner.
+narrateur|Elle s'éloigne.
+narrateur|Elle va vers papa, l'adulte.
+narrateur|Elle souffle.
+enfant-f|Papa, je suis en colère encore.
+papa|Tu as nommé.
+papa|Tu as repris le geste.
+papa|Même leçon, autre lieu.
+papa|Bravo.
+narrateur|La colère a un nom.
+narrateur|Les mains restent loin.
+narrateur|On s'éloigne.
+narrateur|On va vers un adulte.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1348,7 +1419,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La tour de Garance tombe. Que fait-elle de sa colère ?</t>
+          <t>La tour de Nina tombe. Que fait-elle de sa colère ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,7 +1579,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La tour de Garance tombe. Que fait-elle de sa colère ?</t>
+          <t>narrateur|La tour de Nina tombe.
+narrateur|Que fait-elle de sa colère ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1536,7 +1608,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Garance a nommé sa colère. Mains loin. Elle peut s'éloigner. Elle va vers papa, l'adulte.</t>
+          <t>Nina a nommé sa colère. Mains loin. Elle peut s'éloigner. Elle va vers papa, l'adulte. Tu as dit : je suis en colère. Dans la chambre, puis à la cuisine. Bravo, Nina. J'ai ouvert les doigts. Oui. Et tu es venue vers moi. Les cubes restent au sol. Le bois sent encore la forêt.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1680,7 +1752,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Garance a nommé sa colère. Mains loin. Elle peut s'éloigner. Elle va vers papa, l'adulte.</t>
+          <t>narrateur|Nina a nommé sa colère.
+narrateur|Mains loin.
+narrateur|Elle peut s'éloigner.
+narrateur|Elle va vers papa, l'adulte.
+papa|Tu as dit : je suis en colère.
+papa|Dans la chambre, puis à la cuisine.
+papa|Bravo, Nina.
+enfant-f|J'ai ouvert les doigts.
+papa|Oui.
+papa|Et tu es venue vers moi.
+narrateur|Les cubes restent au sol.
+narrateur|Le bois sent encore la forêt.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1708,7 +1791,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Garance s'assoit près de papa. La tour reste au sol.</t>
+          <t>Nina s'assoit près de papa. La tour reste au sol. On laisse les cubes un moment ? Oui, papa. La chaussette attend encore près du lit. Tu as nommé deux fois. C'est du bon travail. Le lait est encore un peu chaud. On le boit tout doux. Tout doux. Le rayon de poussière est plus petit. Les livres restent contre le mur.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,7 +1927,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Garance s'assoit près de papa. La tour reste au sol.</t>
+          <t>narrateur|Nina s'assoit près de papa.
+narrateur|La tour reste au sol.
+papa|On laisse les cubes un moment ?
+enfant-f|Oui, papa.
+narrateur|La chaussette attend encore près du lit.
+papa|Tu as nommé deux fois.
+papa|C'est du bon travail.
+enfant-f|Le lait est encore un peu chaud.
+papa|On le boit tout doux.
+enfant-f|Tout doux.
+narrateur|Le rayon de poussière est plus petit.
+narrateur|Les livres restent contre le mur.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1872,7 +1966,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit : je suis en colère. Je me suis éloignée. Je suis allée vers papa. Bravo, Nina. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,7 +2106,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai dit : je suis en colère.
+enfant-f|Je me suis éloignée.
+enfant-f|Je suis allée vers papa.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2034,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2171,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-07.xlsx
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un rayon jaune traverse la chambre. La poussière danse au-dessus du tapis. Une chaussette attend près du lit. Elle est un peu retournée. Une pile de livres penche contre le mur. Les livres sentent le papier chaud. Des cubes en bois sont au milieu. Le bois sent la forêt, tout doux. Nina, je range les livres. Moi, je fais une tour. Une tour bien droite ? Oui, papa. En ce moment, Nina pose un cube. Puis un autre. La tour monte. Victorino est là, près du tapis. Papa empile encore un livre. Le rouge tout en haut. Tu y es presque. Victorino pose un cube trop vite. La tour tombe. Les cubes roulent. Nina sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Elle ouvre les doigts. Les mains restent loin de Victorino. Nina peut s'éloigner. Elle s'éloigne vers le tapis du lit. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte près des livres. Papa, je suis en colère. La tour est tombée. Tu as dit le nom. Tu es en colère. Bravo, Nina. Tes mains sont restées loin. Tu t'es éloignée. Tu es venue vers moi. Tu as fait du bon travail. Tu veux souffler encore ? Oui, papa. Nina souffle. Le rayon tient encore la poussière. Plus tard, à la cuisine, la table est tiède. Ça sent le lait chaud. Nina a une petite cuillère. Victorino prend la cuillère de Nina. Nina sent encore la chaleur. Elle se souvient. Je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Papa, je suis en colère encore. Tu as nommé. Tu as repris le geste. Même leçon, autre lieu. Bravo. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+          <t>Un rayon jaune traverse la chambre. La poussière danse au-dessus du tapis. Une chaussette attend près du lit. Elle est un peu retournée. Une pile de livres penche contre le mur. Les livres sentent le papier chaud. Des cubes en bois sont au milieu. Le bois sent la forêt, tout doux. Nina, je range les livres. Moi, je fais une tour. Une tour bien droite ? Oui, papa. En ce moment, Nina pose un cube. Puis un autre. La tour monte. Victorino est là, près du tapis. Papa empile encore un livre. Le rouge tout en haut. Tu y es presque. Victorino pose un cube trop vite. La tour tombe. Les cubes roulent. Nina sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Elle ouvre les doigts. Les mains restent loin de Victorino. Nina peut s'éloigner. Elle s'éloigne vers le tapis du lit. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte près des livres. Papa, je suis en colère. La tour est tombée. Tu as dit le nom. Tu es en colère. Bravo, Nina. Tes mains sont restées loin. Tu t'es éloignée. Tu es venue vers moi. Tu veux souffler encore ? Oui, papa. Nina souffle. Le rayon tient encore la poussière. Plus tard, à la cuisine, la table est tiède. Ça sent le lait chaud. Nina a une petite cuillère. Victorino prend la cuillère de Nina. Nina sent encore la chaleur. Elle se souvient. Je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Papa, je suis en colère encore. Tu as nommé. Tu as repris le geste. Même leçon, autre lieu. Bravo. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Garance construit une tour dans la chambre. Papa range des livres. Sami pose un cube trop vite. La tour tombe. Garance sent son visage chaud. Son ventre est dur. Garance dit : je suis en &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt;. Elle ouvre les doigts. Les mains restent loin. Garance peut s'éloigner. Elle s'éloigne vers le tapis. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte. Garance dit : papa, je suis en colère. La tour est tombée. Papa écoute. Plus tard, à la cuisine, Sami prend la cuillère de Garance. Garance sent encore la chaleur. Elle se souvient. Elle dit : je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Papa dit : tu as nommé. Tu as repris le geste. Même leçon, autre lieu. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un rayon jaune traverse la chambre. La poussière danse au-dessus du tapis. Une chaussette attend près du lit. Elle est un peu retournée. Une pile de livres penche contre le mur. Les livres sentent le papier chaud. Des cubes en bois sont au milieu. Le bois sent la forêt, tout doux. Nina, je range les livres. Moi, je fais une tour. Une tour bien droite ? Oui, papa. En ce moment, Nina pose un cube. Puis un autre. La tour monte. Victorino est là, près du tapis. Papa empile encore un livre. Le rouge tout en haut. Tu y es presque. Victorino pose un cube trop vite. La tour tombe. Les cubes roulent. Nina sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Elle ouvre les doigts. Les mains restent loin de Victorino. Nina peut s'éloigner. Elle s'éloigne vers le tapis du lit. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte près des livres. Papa, je suis en colère. La tour est tombée. Tu as dit le nom. Tu es en colère. Bravo, Nina. Tes mains sont restées loin. Tu t'es éloignée. Tu es venue vers moi. Tu veux souffler encore ? Oui, papa. Nina souffle. Le rayon tient encore la poussière. Plus tard, à la cuisine, la table est tiède. Ça sent le lait chaud. Nina a une petite cuillère. Victorino prend la cuillère de Nina. Nina sent encore la chaleur. Elle se souvient. Je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Papa, je suis en colère encore. Tu as nommé. Tu as repris le geste. Même leçon, autre lieu. Bravo. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1366,7 +1366,6 @@
 papa|Tes mains sont restées loin.
 papa|Tu t'es éloignée.
 papa|Tu es venue vers moi.
-papa|Tu as fait du bon travail.
 papa|Tu veux souffler encore ?
 enfant-f|Oui, papa.
 narrateur|Nina souffle.
@@ -1394,7 +1393,6 @@
 narrateur|On va vers un adulte.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1424,7 +1422,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La tour de Garance tombe. Que fait-elle de sa &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt; ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La tour de Nina tombe. Que fait-elle de sa colère ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1583,7 +1581,6 @@
 narrateur|Que fait-elle de sa colère ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1613,7 +1610,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Garance a nommé sa &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt;. Mains loin. Elle peut s'éloigner. Elle va vers papa, l'adulte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a nommé sa colère. Mains loin. Elle peut s'éloigner. Elle va vers papa, l'adulte. Tu as dit : je suis en colère. Dans la chambre, puis à la cuisine. Bravo, Nina. J'ai ouvert les doigts. Oui. Et tu es venue vers moi. Les cubes restent au sol. Le bois sent encore la forêt.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1766,7 +1763,6 @@
 narrateur|Le bois sent encore la forêt.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,12 +1787,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nina s'assoit près de papa. La tour reste au sol. On laisse les cubes un moment ? Oui, papa. La chaussette attend encore près du lit. Tu as nommé deux fois. C'est du bon travail. Le lait est encore un peu chaud. On le boit tout doux. Tout doux. Le rayon de poussière est plus petit. Les livres restent contre le mur.</t>
+          <t>Nina s'assoit près de papa. La tour reste au sol. On laisse les cubes un moment ? Oui, papa. La chaussette attend encore près du lit. Tu as nommé deux fois. Le lait est encore un peu chaud. On le boit tout doux. Tout doux. Le rayon de poussière est plus petit. Les livres restent contre le mur.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Garance s'assoit près de papa. La tour reste au sol.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina s'assoit près de papa. La tour reste au sol. On laisse les cubes un moment ? Oui, papa. La chaussette attend encore près du lit. Tu as nommé deux fois. Le lait est encore un peu chaud. On le boit tout doux. Tout doux. Le rayon de poussière est plus petit. Les livres restent contre le mur.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1933,7 +1929,6 @@
 enfant-f|Oui, papa.
 narrateur|La chaussette attend encore près du lit.
 papa|Tu as nommé deux fois.
-papa|C'est du bon travail.
 enfant-f|Le lait est encore un peu chaud.
 papa|On le boit tout doux.
 enfant-f|Tout doux.
@@ -1941,7 +1936,6 @@
 narrateur|Les livres restent contre le mur.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1966,12 +1960,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit : je suis en colère. Je me suis éloignée. Je suis allée vers papa. Bravo, Nina. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>J'ai dit : je suis en colère. Je me suis éloignée. Je suis allée vers papa. Bravo, Nina.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit : je suis en colère. Je me suis éloignée. Je suis allée vers papa. Bravo, Nina.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2109,12 +2103,9 @@
           <t>enfant-f|J'ai dit : je suis en colère.
 enfant-f|Je me suis éloignée.
 enfant-f|Je suis allée vers papa.
-papa|Bravo, Nina.
-papa|Tu as fait du bon travail.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo, Nina.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2133,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2178,6 +2169,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-07.xlsx
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -684,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Garance, Sami, papa</t>
+          <t>Nina, Victorino, papa</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-07.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nina construit une tour. Un cube tombe. Elle nomme sa colère, s'éloigne, rejoint papa. À la cuisine, la cuillère part. Elle reprend le geste.</t>
+          <t>Nina veut une tour, le cube rouge en haut. Victorino pose trop vite. Elle dit sa colère, recule, rejoint papa. À la cuisine, la cuillère part. Elle recule encore. La tour se relève.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un rayon jaune traverse la chambre. La poussière danse au-dessus du tapis. Une chaussette attend près du lit. Elle est un peu retournée. Une pile de livres penche contre le mur. Les livres sentent le papier chaud. Des cubes en bois sont au milieu. Le bois sent la forêt, tout doux. Nina, je range les livres. Moi, je fais une tour. Une tour bien droite ? Oui, papa. En ce moment, Nina pose un cube. Puis un autre. La tour monte. Victorino est là, près du tapis. Papa empile encore un livre. Le rouge tout en haut. Tu y es presque. Victorino pose un cube trop vite. La tour tombe. Les cubes roulent. Nina sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Elle ouvre les doigts. Les mains restent loin de Victorino. Nina peut s'éloigner. Elle s'éloigne vers le tapis du lit. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte près des livres. Papa, je suis en colère. La tour est tombée. Tu as dit le nom. Tu es en colère. Bravo, Nina. Tes mains sont restées loin. Tu t'es éloignée. Tu es venue vers moi. Tu veux souffler encore ? Oui, papa. Nina souffle. Le rayon tient encore la poussière. Plus tard, à la cuisine, la table est tiède. Ça sent le lait chaud. Nina a une petite cuillère. Victorino prend la cuillère de Nina. Nina sent encore la chaleur. Elle se souvient. Je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Papa, je suis en colère encore. Tu as nommé. Tu as repris le geste. Même leçon, autre lieu. Bravo. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+          <t>Un rayon jaune traverse la chambre. La poussière danse au-dessus du tapis. Une chaussette attend près du lit. Elle est un peu retournée. Une pile de livres penche contre le mur. Les livres sentent le papier chaud. Des cubes en bois sont au milieu. Le bois sent la forêt, tout doux. Nina, je pose les livres. Moi, je fais une tour. Une tour bien droite ? Oui, papa. Le rouge tout en haut. En ce moment, Nina pose un cube. Puis un autre. La tour monte. Victorino est là, près du tapis. Papa empile encore un livre. Encore un, le rouge. Tu y es presque. Victorino pose un cube trop vite. La tour tombe. Les cubes roulent. Nina sent son visage chaud. Son ventre est dur. Je suis en colère. Elle ouvre les doigts. Les mains restent loin de Victorino. Elle recule vers le tapis du lit. Elle souffle trois fois. Puis elle va vers papa. Papa, la tour est tombée. Je t'écoute. Tu veux venir près des livres ? Oui, papa. Nina s'assoit contre la pile. Le papier est tiède sous sa joue. On reste ici un moment ? Un moment. Plus tard, à la cuisine, la table est tiède. Ça sent le lait chaud. Une petite cuillère brille dans le bol. C'est ma cuillère. Le lait est encore un peu chaud. Victorino prend la cuillère de Nina. Le lait tremble dans le bol. Nina sent encore la chaleur au visage. Son ventre se durcit. Elle ouvre encore les doigts. Elle recule vers l'évier. Le carrelage est froid sous ses pieds. Elle va près de papa. Victorino a pris ma cuillère. Je t'écoute. On s'assoit un peu ? Oui. Nina pose les mains sur ses genoux. Le lait fume encore, tout doux. Ta tour t'attend, tu crois ? Oui. Le rouge tout en haut.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Un rayon jaune traverse la chambre. La poussière danse au-dessus du tapis. Une chaussette attend près du lit. Elle est un peu retournée. Une pile de livres penche contre le mur. Les livres sentent le papier chaud. Des cubes en bois sont au milieu. Le bois sent la forêt, tout doux. Nina, je range les livres. Moi, je fais une tour. Une tour bien droite ? Oui, papa. En ce moment, Nina pose un cube. Puis un autre. La tour monte. Victorino est là, près du tapis. Papa empile encore un livre. Le rouge tout en haut. Tu y es presque. Victorino pose un cube trop vite. La tour tombe. Les cubes roulent. Nina sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Elle ouvre les doigts. Les mains restent loin de Victorino. Nina peut s'éloigner. Elle s'éloigne vers le tapis du lit. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte près des livres. Papa, je suis en colère. La tour est tombée. Tu as dit le nom. Tu es en colère. Bravo, Nina. Tes mains sont restées loin. Tu t'es éloignée. Tu es venue vers moi. Tu veux souffler encore ? Oui, papa. Nina souffle. Le rayon tient encore la poussière. Plus tard, à la cuisine, la table est tiède. Ça sent le lait chaud. Nina a une petite cuillère. Victorino prend la cuillère de Nina. Nina sent encore la chaleur. Elle se souvient. Je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Papa, je suis en colère encore. Tu as nommé. Tu as repris le geste. Même leçon, autre lieu. Bravo. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+          <t>Un rayon jaune traverse la chambre. La poussière danse au-dessus du tapis. Une chaussette attend près du lit. Elle est un peu retournée. Une pile de livres penche contre le mur. Les livres sentent le papier chaud. Des cubes en bois sont au milieu. Le bois sent la forêt, tout doux. Nina, je pose les livres. Moi, je fais une tour. Une tour bien droite ? Oui, papa. Le rouge tout en haut. En ce moment, Nina pose un cube. Puis un autre. La tour monte. Victorino est là, près du tapis. Papa empile encore un livre. Encore un, le rouge. Tu y es presque. Victorino pose un cube trop vite. La tour tombe. Les cubes roulent. Nina sent son visage chaud. Son ventre est dur. Je suis en colère. Elle ouvre les doigts. Les mains restent loin de Victorino. Elle recule vers le tapis du lit. Elle souffle trois fois. Puis elle va vers papa. Papa, la tour est tombée. Je t'écoute. Tu veux venir près des livres ? Oui, papa. Nina s'assoit contre la pile. Le papier est tiède sous sa joue. On reste ici un moment ? Un moment. Plus tard, à la cuisine, la table est tiède. Ça sent le lait chaud. Une petite cuillère brille dans le bol. C'est ma cuillère. Le lait est encore un peu chaud. Victorino prend la cuillère de Nina. Le lait tremble dans le bol. Nina sent encore la chaleur au visage. Son ventre se durcit. Elle ouvre encore les doigts. Elle recule vers l'évier. Le carrelage est froid sous ses pieds. Elle va près de papa. Victorino a pris ma cuillère. Je t'écoute. On s'assoit un peu ? Oui. Nina pose les mains sur ses genoux. Le lait fume encore, tout doux. Ta tour t'attend, tu crois ? Oui. Le rouge tout en haut.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1332,64 +1332,59 @@
 narrateur|Les livres sentent le papier chaud.
 narrateur|Des cubes en bois sont au milieu.
 narrateur|Le bois sent la forêt, tout doux.
-papa|Nina, je range les livres.
+papa|Nina, je pose les livres.
 enfant-f|Moi, je fais une tour.
 papa|Une tour bien droite ?
 enfant-f|Oui, papa.
+enfant-f|Le rouge tout en haut.
 narrateur|En ce moment, Nina pose un cube.
 narrateur|Puis un autre.
 narrateur|La tour monte.
 narrateur|Victorino est là, près du tapis.
 narrateur|Papa empile encore un livre.
-enfant-f|Le rouge tout en haut.
+enfant-f|Encore un, le rouge.
 papa|Tu y es presque.
 narrateur|Victorino pose un cube trop vite.
 narrateur|La tour tombe.
 narrateur|Les cubes roulent.
 narrateur|Nina sent son visage chaud.
 narrateur|Son ventre est dur.
-narrateur|Être en colère, ce n'est pas honteux.
 enfant-f|Je suis en colère.
 narrateur|Elle ouvre les doigts.
 narrateur|Les mains restent loin de Victorino.
-narrateur|Nina peut s'éloigner.
-narrateur|Elle s'éloigne vers le tapis du lit.
+narrateur|Elle recule vers le tapis du lit.
 narrateur|Elle souffle trois fois.
 narrateur|Puis elle va vers papa.
-narrateur|Papa est l'adulte près des livres.
-enfant-f|Papa, je suis en colère.
-enfant-f|La tour est tombée.
-papa|Tu as dit le nom.
-papa|Tu es en colère.
-papa|Bravo, Nina.
-papa|Tes mains sont restées loin.
-papa|Tu t'es éloignée.
-papa|Tu es venue vers moi.
-papa|Tu veux souffler encore ?
+enfant-f|Papa, la tour est tombée.
+papa|Je t'écoute.
+papa|Tu veux venir près des livres ?
 enfant-f|Oui, papa.
-narrateur|Nina souffle.
-narrateur|Le rayon tient encore la poussière.
+narrateur|Nina s'assoit contre la pile.
+narrateur|Le papier est tiède sous sa joue.
+papa|On reste ici un moment ?
+enfant-f|Un moment.
 narrateur|Plus tard, à la cuisine, la table est tiède.
 narrateur|Ça sent le lait chaud.
-narrateur|Nina a une petite cuillère.
+narrateur|Une petite cuillère brille dans le bol.
+enfant-f|C'est ma cuillère.
+papa|Le lait est encore un peu chaud.
 narrateur|Victorino prend la cuillère de Nina.
-narrateur|Nina sent encore la chaleur.
-narrateur|Elle se souvient.
-enfant-f|Je suis en colère.
-narrateur|Les mains restent loin.
-narrateur|Elle peut s'éloigner.
-narrateur|Elle s'éloigne.
-narrateur|Elle va vers papa, l'adulte.
-narrateur|Elle souffle.
-enfant-f|Papa, je suis en colère encore.
-papa|Tu as nommé.
-papa|Tu as repris le geste.
-papa|Même leçon, autre lieu.
-papa|Bravo.
-narrateur|La colère a un nom.
-narrateur|Les mains restent loin.
-narrateur|On s'éloigne.
-narrateur|On va vers un adulte.</t>
+narrateur|Le lait tremble dans le bol.
+narrateur|Nina sent encore la chaleur au visage.
+narrateur|Son ventre se durcit.
+narrateur|Elle ouvre encore les doigts.
+narrateur|Elle recule vers l'évier.
+narrateur|Le carrelage est froid sous ses pieds.
+narrateur|Elle va près de papa.
+enfant-f|Victorino a pris ma cuillère.
+papa|Je t'écoute.
+papa|On s'assoit un peu ?
+enfant-f|Oui.
+narrateur|Nina pose les mains sur ses genoux.
+narrateur|Le lait fume encore, tout doux.
+papa|Ta tour t'attend, tu crois ?
+enfant-f|Oui.
+enfant-f|Le rouge tout en haut.</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1411,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La tour de Nina tombe. Que fait-elle de sa colère ?</t>
+          <t>La tour de Nina tombe. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>La tour de Nina tombe. Que fait-elle de sa colère ?</t>
+          <t>La tour de Nina tombe. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1451,7 +1446,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Garance nomme sa colère. Puis elle va où ?</t>
+          <t>Nina ouvre les doigts. Puis elle va où ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1493,14 +1488,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1577,7 +1572,7 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|La tour de Nina tombe.
-narrateur|Que fait-elle de sa colère ?</t>
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1599,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a nommé sa colère. Mains loin. Elle peut s'éloigner. Elle va vers papa, l'adulte. Tu as dit : je suis en colère. Dans la chambre, puis à la cuisine. Bravo, Nina. J'ai ouvert les doigts. Oui. Et tu es venue vers moi. Les cubes restent au sol. Le bois sent encore la forêt.</t>
+          <t>Nina revient près du tapis. Les cubes sont épars, un peu tièdes. On reprend le rouge ? Tout en haut. Victorino pousse un cube vers elle. Nina pose, puis pose encore. La tour se relève. Bravo, Nina. Elle tient. Oui. Le rayon tient encore la poussière. La chaussette attend près du lit.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Nina a nommé sa colère. Mains loin. Elle peut s'éloigner. Elle va vers papa, l'adulte. Tu as dit : je suis en colère. Dans la chambre, puis à la cuisine. Bravo, Nina. J'ai ouvert les doigts. Oui. Et tu es venue vers moi. Les cubes restent au sol. Le bois sent encore la forêt.</t>
+          <t>Nina revient près du tapis. Les cubes sont épars, un peu tièdes. On reprend le rouge ? Tout en haut. Victorino pousse un cube vers elle. Nina pose, puis pose encore. La tour se relève. Bravo, Nina. Elle tient. Oui. Le rayon tient encore la poussière. La chaussette attend près du lit.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1672,7 +1667,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1748,18 +1743,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nina a nommé sa colère.
-narrateur|Mains loin.
-narrateur|Elle peut s'éloigner.
-narrateur|Elle va vers papa, l'adulte.
-papa|Tu as dit : je suis en colère.
-papa|Dans la chambre, puis à la cuisine.
+          <t>narrateur|Nina revient près du tapis.
+narrateur|Les cubes sont épars, un peu tièdes.
+papa|On reprend le rouge ?
+enfant-f|Tout en haut.
+narrateur|Victorino pousse un cube vers elle.
+narrateur|Nina pose, puis pose encore.
+narrateur|La tour se relève.
 papa|Bravo, Nina.
-enfant-f|J'ai ouvert les doigts.
+enfant-f|Elle tient.
 papa|Oui.
-papa|Et tu es venue vers moi.
-narrateur|Les cubes restent au sol.
-narrateur|Le bois sent encore la forêt.</t>
+narrateur|Le rayon tient encore la poussière.
+narrateur|La chaussette attend près du lit.</t>
         </is>
       </c>
     </row>
@@ -1786,12 +1781,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nina s'assoit près de papa. La tour reste au sol. On laisse les cubes un moment ? Oui, papa. La chaussette attend encore près du lit. Tu as nommé deux fois. Le lait est encore un peu chaud. On le boit tout doux. Tout doux. Le rayon de poussière est plus petit. Les livres restent contre le mur.</t>
+          <t>Nina s'assoit près de papa. Le lait n'est plus trop chaud. Tu goûtes, tout doux ? Oui, papa. La cuillère revient dans le bol. Le rouge est en haut. Il brille un peu. Les livres restent droits contre le mur. Le bois des cubes sent encore la forêt.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Nina s'assoit près de papa. La tour reste au sol. On laisse les cubes un moment ? Oui, papa. La chaussette attend encore près du lit. Tu as nommé deux fois. Le lait est encore un peu chaud. On le boit tout doux. Tout doux. Le rayon de poussière est plus petit. Les livres restent contre le mur.</t>
+          <t>Nina s'assoit près de papa. Le lait n'est plus trop chaud. Tu goûtes, tout doux ? Oui, papa. La cuillère revient dans le bol. Le rouge est en haut. Il brille un peu. Les livres restent droits contre le mur. Le bois des cubes sent encore la forêt.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1854,7 +1849,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1923,16 +1918,14 @@
       <c r="AW5" t="inlineStr">
         <is>
           <t>narrateur|Nina s'assoit près de papa.
-narrateur|La tour reste au sol.
-papa|On laisse les cubes un moment ?
+narrateur|Le lait n'est plus trop chaud.
+papa|Tu goûtes, tout doux ?
 enfant-f|Oui, papa.
-narrateur|La chaussette attend encore près du lit.
-papa|Tu as nommé deux fois.
-enfant-f|Le lait est encore un peu chaud.
-papa|On le boit tout doux.
-enfant-f|Tout doux.
-narrateur|Le rayon de poussière est plus petit.
-narrateur|Les livres restent contre le mur.</t>
+narrateur|La cuillère revient dans le bol.
+enfant-f|Le rouge est en haut.
+papa|Il brille un peu.
+narrateur|Les livres restent droits contre le mur.
+narrateur|Le bois des cubes sent encore la forêt.</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit : je suis en colère. Je me suis éloignée. Je suis allée vers papa. Bravo, Nina.</t>
+          <t>Ma tour est droite. Merci, Nina. Le cube rouge reste tout en haut. Le rayon jaune glisse sur le bois.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit : je suis en colère. Je me suis éloignée. Je suis allée vers papa. Bravo, Nina.</t>
+          <t>Ma tour est droite. Merci, Nina. Le cube rouge reste tout en haut. Le rayon jaune glisse sur le bois.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2027,7 +2020,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2099,10 +2092,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|J'ai dit : je suis en colère.
-enfant-f|Je me suis éloignée.
-enfant-f|Je suis allée vers papa.
-papa|Bravo, Nina.</t>
+          <t>enfant-f|Ma tour est droite.
+papa|Merci, Nina.
+narrateur|Le cube rouge reste tout en haut.
+narrateur|Le rayon jaune glisse sur le bois.</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2173,6 +2166,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
